--- a/output/pdf_financials_xlsx/GDV.xlsx
+++ b/output/pdf_financials_xlsx/GDV.xlsx
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.025089</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.878927</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.517618</v>
       </c>
     </row>
     <row r="35">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.025089</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.878927</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.517618</v>
       </c>
     </row>
     <row r="37">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/GDV.xlsx
+++ b/output/pdf_financials_xlsx/GDV.xlsx
@@ -6163,7 +6163,11 @@
           <t>Net investment income (loss) before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>0.573047</v>
       </c>
@@ -6190,7 +6194,11 @@
           <t>Distributions on Preferred shares (note 6)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>-1.853581</v>
       </c>
